--- a/Master_Data_Casting.xlsx
+++ b/Master_Data_Casting.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phummarin_r\Desktop\SMART MO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99E4F3F-B3DF-406A-9EFB-7942334F9E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A8D85A-63C9-4EF5-92DC-A1A00DD60A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Schedule_Routing_Reference" sheetId="4" r:id="rId1"/>
+    <sheet name="Item_Master" sheetId="4" r:id="rId1"/>
     <sheet name="Supplier_Allocation" sheetId="3" r:id="rId2"/>
     <sheet name="Transaction_Log" sheetId="5" r:id="rId3"/>
   </sheets>
